--- a/Result/profitability/3592.xlsx
+++ b/Result/profitability/3592.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>10.91</v>
       </c>
       <c r="M2" t="n">
-        <v>5.69375</v>
+        <v>5.37625</v>
       </c>
       <c r="N2" t="n">
-        <v>28.23375</v>
+        <v>27.6675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>5.55875</v>
+        <v>5.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>27.495</v>
+        <v>27.01625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.51</v>
       </c>
       <c r="M4" t="n">
-        <v>5.30875</v>
+        <v>5.119999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>26.645</v>
+        <v>26.1675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>10.08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8125</v>
+        <v>5.9425</v>
       </c>
       <c r="N5" t="n">
-        <v>26.5525</v>
+        <v>26.40375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>15.47</v>
       </c>
       <c r="M6" t="n">
-        <v>7.30875</v>
+        <v>7.31</v>
       </c>
       <c r="N6" t="n">
-        <v>26.765</v>
+        <v>26.4</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>13.08</v>
       </c>
       <c r="M7" t="n">
-        <v>8.3775</v>
+        <v>8.42625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.59875</v>
+        <v>26.18375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>6.89</v>
       </c>
       <c r="M8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="N8" t="n">
-        <v>25.66625</v>
+        <v>25.30875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -6778,6 +6778,133 @@
       </c>
       <c r="AM50" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6821</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5067</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F51" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="G51" t="n">
+        <v>354</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>39</v>
+      </c>
+      <c r="J51" t="n">
+        <v>393</v>
+      </c>
+      <c r="K51" t="n">
+        <v>344</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.8975</v>
+      </c>
+      <c r="N51" t="n">
+        <v>28.52875</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.1884816753926701</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-2.859999999999999</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-0.1000699790062981</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.2971428571428572</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-1.190000000000001</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>-0.04422147900408779</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
